--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 18/06/2026, 11:47</x:t>
+    <x:t>Conta: 5166121 | 23/06/2026, 13:57</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,69 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>99,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 818.956,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,80%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 901,15</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/05/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/06/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDI 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>505.218,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 813.401,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 817.706,64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,11%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 911,11</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -124,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>911,11</x:t>
+    <x:t>901,15</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -668,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -728,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>819867.77531098</x:v>
+        <x:v>901.15</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>818956.66531098</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>911.11</x:v>
+        <x:v>901.15</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -782,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -798,192 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 23/06/2026, 13:57</x:t>
+    <x:t>Conta: 5166121 | 24/06/2026, 16:30</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 24/06/2026, 16:30</x:t>
+    <x:t>Conta: 5166121 | 26/06/2026, 17:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 26/06/2026, 17:04</x:t>
+    <x:t>Conta: 5166121 | 29/06/2026, 11:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 29/06/2026, 11:43</x:t>
+    <x:t>Conta: 5166121 | 30/06/2026, 20:06</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 30/06/2026, 20:06</x:t>
+    <x:t>Conta: 5166121 | 01/07/2026, 18:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 01/07/2026, 18:17</x:t>
+    <x:t>Conta: 5166121 | 03/07/2026, 15:19</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 03/07/2026, 15:19</x:t>
+    <x:t>Conta: 5166121 | 06/07/2026, 17:13</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 06/07/2026, 17:13</x:t>
+    <x:t>Conta: 5166121 | 07/07/2026, 15:54</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 07/07/2026, 15:54</x:t>
+    <x:t>Conta: 5166121 | 09/07/2026, 18:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 09/07/2026, 18:04</x:t>
+    <x:t>Conta: 5166121 | 14/07/2026, 09:57</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 901,15</x:t>
+    <x:t>R$ 1.251,44</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -70,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>901,15</x:t>
+    <x:t>1251,44</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -674,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>901.15</x:v>
+        <x:v>1251.44</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>901.15</x:v>
+        <x:v>1251.44</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 14/07/2026, 09:57</x:t>
+    <x:t>Conta: 5166121 | 15/07/2026, 19:00</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,60 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.251,44</x:t>
+    <x:t>100%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.251,44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100,00%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.346,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -68,9 +113,6 @@
   </x:si>
   <x:si>
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1251,44</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -614,10 +656,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.996339" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -674,13 +716,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1251.44</x:v>
+        <x:v>2001251.43998678</x:v>
       </x:c>
       <x:c r="B4" s="7">
+        <x:v>2001251.43998678</x:v>
+      </x:c>
+      <x:c r="C4" s="7">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="7">
-        <x:v>1251.44</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +770,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,86 +786,192 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="C10" s="12"/>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 15/07/2026, 19:00</x:t>
+    <x:t>Conta: 5166121 | 21/07/2026, 09:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,52 +37,58 @@
     <x:t>100%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 2.004.828,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100,00%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garantia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.346,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 2.001.251,44</x:t>
   </x:si>
   <x:si>
-    <x:t>100,00%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Garantia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.346,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
+    <x:t>R$ 2.004.023,41</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
@@ -716,10 +722,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2001251.43998678</x:v>
+        <x:v>2004828.17783348</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2001251.43998678</x:v>
+        <x:v>2004828.17783348</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>
@@ -843,13 +849,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
@@ -880,7 +886,7 @@
       <x:c r="I12" s="9"/>
       <x:c r="J12" s="9"/>
       <x:c r="K12" s="10" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -904,66 +910,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H14" s="11" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I14" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J14" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
       <x:c r="A15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K15" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 21/07/2026, 09:17</x:t>
+    <x:t>Conta: 5166121 | 27/07/2026, 15:22</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.004.828,18</x:t>
+    <x:t>R$ 2.008.411,31</x:t>
   </x:si>
   <x:si>
     <x:t>100,00%|Pós-Fixada</x:t>
@@ -88,7 +88,7 @@
     <x:t>R$ 2.001.251,44</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.004.023,41</x:t>
+    <x:t>R$ 2.006.800,34</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
@@ -722,10 +722,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2004828.17783348</x:v>
+        <x:v>2008411.3081976</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2004828.17783348</x:v>
+        <x:v>2008411.3081976</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 27/07/2026, 15:22</x:t>
+    <x:t>Conta: 5166121 | 29/07/2026, 18:27</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.008.411,31</x:t>
+    <x:t>R$ 2.010.205,27</x:t>
   </x:si>
   <x:si>
     <x:t>100,00%|Pós-Fixada</x:t>
@@ -88,7 +88,7 @@
     <x:t>R$ 2.001.251,44</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.006.800,34</x:t>
+    <x:t>R$ 2.008.190,66</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
@@ -722,10 +722,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2008411.3081976</x:v>
+        <x:v>2010205.27414564</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2008411.3081976</x:v>
+        <x:v>2010205.27414564</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 29/07/2026, 18:27</x:t>
+    <x:t>Conta: 5166121 | 30/07/2026, 16:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,66 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.010.205,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100,00%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 886,30</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.346,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.251,44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.008.190,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -119,6 +68,9 @@
   </x:si>
   <x:si>
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>886,3</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -662,10 +614,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -722,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2010205.27414564</x:v>
+        <x:v>886.3</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2010205.27414564</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0</x:v>
+        <x:v>886.3</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -776,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -792,192 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 30/07/2026, 16:37</x:t>
+    <x:t>Conta: 5166121 | 04/08/2026, 17:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,87 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 886,30</x:t>
+    <x:t>100,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.503.119,25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>882.352,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.339,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.038,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.187,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.886,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.779,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.578,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,30</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +142,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>886,3</x:t>
+    <x:t>0,3</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -266,7 +338,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -312,6 +384,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -614,7 +690,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -674,13 +750,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>886.3</x:v>
+        <x:v>3503119.55353596</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>3503119.25353596</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>886.3</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +804,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,86 +820,221 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="C10" s="12"/>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A11" s="13"/>
+      <x:c r="B11" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J11" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="9"/>
+      <x:c r="H13" s="9"/>
+      <x:c r="I13" s="9"/>
+      <x:c r="J13" s="9"/>
+      <x:c r="K13" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A13:J13"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 04/08/2026, 17:40</x:t>
+    <x:t>Conta: 5166121 | 11/08/2026, 16:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.503.119,25</x:t>
+    <x:t>R$ 9.917.404,67</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -79,19 +79,19 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>882.352,00</x:t>
+    <x:t>235.850,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.339,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.038,37</x:t>
+    <x:t>R$ 400.945,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 402.191,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 401.911,03</x:t>
   </x:si>
   <x:si>
     <x:t>03/08/2026</x:t>
@@ -106,13 +106,46 @@
     <x:t>R$ 2.000.886,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.779,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.578,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,30</x:t>
+    <x:t>R$ 2.006.207,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.010,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.288,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.507.248,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.505.617,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.162.790,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.756,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.361,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4,00</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -142,7 +175,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>0,3</x:t>
+    <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -690,7 +723,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K16"/>
+  <x:dimension ref="A1:K18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -750,13 +783,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3503119.55353596</x:v>
+        <x:v>9917408.67083902</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3503119.25353596</x:v>
+        <x:v>9917404.67083902</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0.3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -888,63 +921,91 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13" t="s">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13" t="s">
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="s">
+      <x:c r="E11" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="F11" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="G11" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H11" s="13" t="s">
+      <x:c r="H11" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="s">
+      <x:c r="I11" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="s">
+      <x:c r="J11" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="9"/>
-      <x:c r="J13" s="9"/>
-      <x:c r="K13" s="10" t="s">
+    <x:row r="12" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="C12" s="12"/>
+      <x:c r="D12" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A13" s="13"/>
+      <x:c r="B13" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="13"/>
+      <x:c r="D13" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J13" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K13" s="3"/>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="4"/>
@@ -959,74 +1020,104 @@
       <x:c r="J14" s="4"/>
       <x:c r="K14" s="4"/>
     </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
+    <x:row r="15" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A15" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
+      <x:c r="D15" s="9"/>
+      <x:c r="E15" s="9"/>
+      <x:c r="F15" s="9"/>
+      <x:c r="G15" s="9"/>
+      <x:c r="H15" s="9"/>
+      <x:c r="I15" s="9"/>
+      <x:c r="J15" s="9"/>
+      <x:c r="K15" s="10" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A17" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B17" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>43</x:v>
+      <x:c r="C17" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K17" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K18" s="13" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1034,7 +1125,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:J13"/>
+    <x:mergeCell ref="A15:J15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 11/08/2026, 16:37</x:t>
+    <x:t>Conta: 5166121 | 17/08/2026, 14:25</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 9.917.404,67</x:t>
+    <x:t>R$ 9.934.835,48</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 400.945,43</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 402.191,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 401.911,03</x:t>
+    <x:t>R$ 402.898,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 402.458,87</x:t>
   </x:si>
   <x:si>
     <x:t>03/08/2026</x:t>
@@ -106,10 +106,10 @@
     <x:t>R$ 2.000.886,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.006.207,98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.010,53</x:t>
+    <x:t>R$ 2.009.734,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.007.743,27</x:t>
   </x:si>
   <x:si>
     <x:t>06/08/2026</x:t>
@@ -124,10 +124,10 @@
     <x:t>R$ 5.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.507.248,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.505.617,59</x:t>
+    <x:t>R$ 5.516.928,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.513.119,22</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
@@ -139,13 +139,13 @@
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.756,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.361,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4,00</x:t>
+    <x:t>R$ 2.005.275,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.004.088,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 381,90</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -175,7 +175,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
+    <x:t>381,9</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -783,13 +783,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>9917408.67083902</x:v>
+        <x:v>9935217.38182206</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>9917404.67083902</x:v>
+        <x:v>9934835.48182206</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>4</x:v>
+        <x:v>381.9</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 17/08/2026, 14:25</x:t>
+    <x:t>Conta: 5166121 | 18/08/2026, 09:39</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 9.934.835,48</x:t>
+    <x:t>R$ 11.339.177,11</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -70,46 +70,28 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>31/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/09/2026</x:t>
+    <x:t>03/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>235.850,00</x:t>
+    <x:t>4.677,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 400.945,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 402.898,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 402.458,87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.187,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.886,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.009.734,09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.007.743,27</x:t>
+    <x:t>R$ 1.804.153,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.812.927,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.810.953,15</x:t>
   </x:si>
   <x:si>
     <x:t>06/08/2026</x:t>
@@ -124,28 +106,46 @@
     <x:t>R$ 5.500.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.516.928,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.513.119,22</x:t>
+    <x:t>R$ 5.519.350,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.514.996,68</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>1.162.790,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.275,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.004.088,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 381,90</x:t>
+    <x:t>1.162.712,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.865,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.006.021,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.004.636,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.265.822,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.878,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.680,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 382,03</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -175,7 +175,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>381,9</x:t>
+    <x:t>382,03</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -783,13 +783,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>9935217.38182206</x:v>
+        <x:v>11339559.1368124</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>9934835.48182206</x:v>
+        <x:v>11339177.1068124</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>381.9</x:v>
+        <x:v>382.03</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -956,36 +956,36 @@
       </x:c>
       <x:c r="C12" s="12"/>
       <x:c r="D12" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="s">
+      <x:c r="J12" s="12" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
     <x:row r="13" spans="1:11" ht="30" customHeight="1">
       <x:c r="A13" s="13"/>
       <x:c r="B13" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="13"/>
       <x:c r="D13" s="13" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
         <x:v>20</x:v>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 18/08/2026, 09:39</x:t>
+    <x:t>Conta: 5166121 | 18/08/2026, 18:42</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.339.177,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
+    <x:t>67,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.334.684,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,61 +70,43 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>03/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/09/2026</x:t>
+    <x:t>06/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>4.677,00</x:t>
+    <x:t>2.231,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.804.153,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.812.927,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.810.953,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.288,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.500.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.519.350,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.514.996,68</x:t>
+    <x:t>R$ 2.320.442,51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.328.606,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.326.769,60</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>1.162.712,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.865,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.006.021,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.004.636,14</x:t>
+    <x:t>1.162.237,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.048,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.201,56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.817,20</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -133,19 +115,22 @@
     <x:t>18/09/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>1.265.822,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.999.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.878,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.680,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 382,03</x:t>
+    <x:t>1.265.821,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.999.998,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.876,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.679,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,1%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.000.382,83</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -175,7 +160,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>382,03</x:t>
+    <x:t>3000382,83</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -723,7 +708,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K18"/>
+  <x:dimension ref="A1:K17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -783,13 +768,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11339559.1368124</x:v>
+        <x:v>9335067.49512979</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11339177.1068124</x:v>
+        <x:v>6334684.66512979</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>382.03</x:v>
+        <x:v>3000382.83</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -927,197 +912,168 @@
       </x:c>
       <x:c r="C11" s="12"/>
       <x:c r="D11" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E11" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G11" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H11" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="s">
+      <x:c r="J11" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="s">
+      <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A12" s="13"/>
+      <x:c r="B12" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A12" s="12"/>
-      <x:c r="B12" s="12" t="s">
+      <x:c r="C12" s="13"/>
+      <x:c r="D12" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="12"/>
-      <x:c r="D12" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="12" t="s">
+      <x:c r="E12" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="s">
+      <x:c r="F12" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="s">
+      <x:c r="G12" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="s">
+      <x:c r="H12" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="s">
+      <x:c r="I12" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="s">
+      <x:c r="J12" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="K12" s="3"/>
     </x:row>
-    <x:row r="13" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A13" s="13"/>
-      <x:c r="B13" s="13" t="s">
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A14" s="8" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C13" s="13"/>
-      <x:c r="D13" s="13" t="s">
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="9"/>
+      <x:c r="E14" s="9"/>
+      <x:c r="F14" s="9"/>
+      <x:c r="G14" s="9"/>
+      <x:c r="H14" s="9"/>
+      <x:c r="I14" s="9"/>
+      <x:c r="J14" s="9"/>
+      <x:c r="K14" s="10" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F13" s="13" t="s">
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A16" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H13" s="13" t="s">
+      <x:c r="D16" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I13" s="13" t="s">
+      <x:c r="E16" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J13" s="13" t="s">
+      <x:c r="F16" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K13" s="3"/>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A15" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B15" s="9"/>
-      <x:c r="C15" s="9"/>
-      <x:c r="D15" s="9"/>
-      <x:c r="E15" s="9"/>
-      <x:c r="F15" s="9"/>
-      <x:c r="G15" s="9"/>
-      <x:c r="H15" s="9"/>
-      <x:c r="I15" s="9"/>
-      <x:c r="J15" s="9"/>
-      <x:c r="K15" s="10" t="s">
+      <x:c r="G16" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A17" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="H16" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="s">
+      <x:c r="I16" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="J16" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="K16" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H17" s="11" t="s">
+      <x:c r="B17" s="13" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J17" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K17" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K18" s="13" t="s">
-        <x:v>54</x:v>
+      <x:c r="C17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K17" s="13" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1125,7 +1081,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A15:J15"/>
+    <x:mergeCell ref="A14:J14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 18/08/2026, 18:42</x:t>
+    <x:t>Conta: 5166121 | 18/08/2026, 18:52</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>67,9%|Operações Compromissadas</x:t>
+    <x:t>55,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 6.334.684,67</x:t>
   </x:si>
   <x:si>
-    <x:t>67,80%|Pós-Fixada</x:t>
+    <x:t>55,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -127,7 +127,43 @@
     <x:t>R$ 2.000.679,02</x:t>
   </x:si>
   <x:si>
-    <x:t>32,1%|Saldo projetado</x:t>
+    <x:t>17,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.363,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,5%|Saldo projetado</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 3.000.382,83</x:t>
@@ -708,10 +744,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K17"/>
+  <x:dimension ref="A1:K22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -768,10 +804,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>9335067.49512979</x:v>
+        <x:v>11335067.4951298</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6334684.66512979</x:v>
+        <x:v>8334684.66512979</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>3000382.83</x:v>
@@ -985,13 +1021,13 @@
       <x:c r="D14" s="9"/>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
-      <x:c r="G14" s="9"/>
-      <x:c r="H14" s="9"/>
-      <x:c r="I14" s="9"/>
-      <x:c r="J14" s="9"/>
-      <x:c r="K14" s="10" t="s">
+      <x:c r="G14" s="10" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
+      <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="4"/>
@@ -1001,87 +1037,185 @@
       <x:c r="E15" s="4"/>
       <x:c r="F15" s="4"/>
       <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
+      <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A16" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G16" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
       <x:c r="A17" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B17" s="13" t="s">
+      <x:c r="F17" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K17" s="13" t="s">
-        <x:v>49</x:v>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="9"/>
+      <x:c r="H19" s="9"/>
+      <x:c r="I19" s="9"/>
+      <x:c r="J19" s="9"/>
+      <x:c r="K19" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K21" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K22" s="13" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A14:J14"/>
+    <x:mergeCell ref="A14:F14"/>
+    <x:mergeCell ref="A19:J19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 18/08/2026, 18:52</x:t>
+    <x:t>Conta: 5166121 | 20/08/2026, 09:48</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,10 +37,10 @@
     <x:t>55,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.334.684,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,80%|Pós-Fixada</x:t>
+    <x:t>R$ 6.340.249,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 2.320.442,51</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.328.606,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.326.769,60</x:t>
+    <x:t>R$ 2.330.651,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.328.354,83</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
@@ -103,10 +103,10 @@
     <x:t>R$ 1.999.048,84</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.005.201,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.817,20</x:t>
+    <x:t>R$ 2.006.962,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.182,27</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -121,52 +121,79 @@
     <x:t>R$ 1.999.998,41</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.876,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.679,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,6%|Fundos de Investimento</x:t>
+    <x:t>R$ 2.002.634,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.041,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.001.067,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.363,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.067,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.033,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.438,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 2.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>17,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qtd. cotas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Em cotização</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 271,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.363,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26,5%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.000.382,83</x:t>
+    <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>680.719,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 382,83</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -196,7 +223,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>3000382,83</x:t>
+    <x:t>382,83</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -744,7 +771,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K22"/>
+  <x:dimension ref="A1:K24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -804,13 +831,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11335067.4951298</x:v>
+        <x:v>11341699.4487881</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8334684.66512979</x:v>
+        <x:v>11341316.6187881</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>3000382.83</x:v>
+        <x:v>382.83</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1070,61 +1097,85 @@
       <x:c r="K16" s="3"/>
     </x:row>
     <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="13" t="s">
+      <x:c r="A17" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B17" s="13" t="s">
+      <x:c r="B17" s="12" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="s">
+      <x:c r="C17" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D17" s="13" t="s">
+      <x:c r="D17" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E17" s="13" t="s">
+      <x:c r="E17" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>38</x:v>
+      <x:c r="F17" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
       <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="9"/>
-      <x:c r="H19" s="9"/>
-      <x:c r="I19" s="9"/>
-      <x:c r="J19" s="9"/>
-      <x:c r="K19" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="3"/>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="4"/>
@@ -1139,74 +1190,104 @@
       <x:c r="J20" s="4"/>
       <x:c r="K20" s="4"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
+    <x:row r="21" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A21" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="9"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="G21" s="9"/>
+      <x:c r="H21" s="9"/>
+      <x:c r="I21" s="9"/>
+      <x:c r="J21" s="9"/>
+      <x:c r="K21" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A23" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="s">
+      <x:c r="B23" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J21" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K21" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
+      <x:c r="C23" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
+      <x:c r="D23" s="11" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="I22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J22" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K22" s="13" t="s">
-        <x:v>61</x:v>
+      <x:c r="E23" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K23" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J24" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K24" s="13" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1215,7 +1296,7 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A14:F14"/>
-    <x:mergeCell ref="A19:J19"/>
+    <x:mergeCell ref="A21:J21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 5166121.xlsx
+++ b/data/positions/Posição Consolidada - 5166121.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 5166121 | 20/08/2026, 09:48</x:t>
+    <x:t>Conta: 5166121 | 21/08/2026, 14:50</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,10 +37,10 @@
     <x:t>55,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 6.340.249,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,90%|Pós-Fixada</x:t>
+    <x:t>R$ 6.343.033,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 2.320.442,51</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.330.651,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.328.354,83</x:t>
+    <x:t>R$ 2.331.675,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.329.147,99</x:t>
   </x:si>
   <x:si>
     <x:t>07/08/2026</x:t>
@@ -103,10 +103,10 @@
     <x:t>R$ 1.999.048,84</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.006.962,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.182,27</x:t>
+    <x:t>R$ 2.007.844,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.865,27</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -121,19 +121,19 @@
     <x:t>R$ 1.999.998,41</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.002.634,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.041,15</x:t>
+    <x:t>R$ 2.003.513,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.722,67</x:t>
   </x:si>
   <x:si>
     <x:t>44,1%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.001.067,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 5.005.110,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -151,10 +151,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>19/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 271,75</x:t>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,88</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -163,22 +163,28 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.067,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.033,10</x:t>
+    <x:t>R$ 2.002.066,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.112,10</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.438,19</x:t>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.439,63</x:t>
   </x:si>
   <x:si>
     <x:t>1.390,64</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
+    <x:t>R$ 2.002.002,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.108,63</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
@@ -190,7 +196,10 @@
     <x:t>680.719,86</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.000.000,00</x:t>
+    <x:t>R$ 1.001.041,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.056,52</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 382,83</x:t>
@@ -831,10 +840,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11341699.4487881</x:v>
+        <x:v>11348526.6076973</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11341316.6187881</x:v>
+        <x:v>11348143.7776973</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>382.83</x:v>
@@ -1128,22 +1137,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1152,25 +1161,25 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
       <x:c r="A19" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D19" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E19" s="13" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G19" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1204,7 +1213,7 @@
       <x:c r="I21" s="9"/>
       <x:c r="J21" s="9"/>
       <x:c r="K21" s="10" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1228,66 +1237,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E23" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F23" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G23" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H23" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I23" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J23" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K23" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K24" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
